--- a/artfynd/A 65184-2023 artfynd.xlsx
+++ b/artfynd/A 65184-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2532,6 +2532,228 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120135690</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kuuravaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>865203</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7411883</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk, Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120136766</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91832</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kuuravaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>865186</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7411902</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk, Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 65184-2023 artfynd.xlsx
+++ b/artfynd/A 65184-2023 artfynd.xlsx
@@ -2537,7 +2537,7 @@
         <v>120135690</v>
       </c>
       <c r="B18" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>120136766</v>
       </c>
       <c r="B19" t="n">
-        <v>91832</v>
+        <v>91850</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 65184-2023 artfynd.xlsx
+++ b/artfynd/A 65184-2023 artfynd.xlsx
@@ -2643,7 +2643,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 65184-2023 artfynd.xlsx
+++ b/artfynd/A 65184-2023 artfynd.xlsx
@@ -2534,10 +2534,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120135690</v>
+        <v>120136766</v>
       </c>
       <c r="B18" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2546,25 +2546,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>865203</v>
+        <v>865186</v>
       </c>
       <c r="R18" t="n">
-        <v>7411883</v>
+        <v>7411902</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2610,19 +2610,9 @@
           <t>2024-09-13</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>16:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2643,17 +2633,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120136766</v>
+        <v>120135690</v>
       </c>
       <c r="B19" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2662,25 +2652,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2693,10 +2683,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>865186</v>
+        <v>865203</v>
       </c>
       <c r="R19" t="n">
-        <v>7411902</v>
+        <v>7411883</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2726,9 +2716,19 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 65184-2023 artfynd.xlsx
+++ b/artfynd/A 65184-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116795753</v>
+        <v>116796929</v>
       </c>
       <c r="B2" t="n">
-        <v>56494</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>865167</v>
+        <v>865226</v>
       </c>
       <c r="R2" t="n">
-        <v>7411978</v>
+        <v>7411810</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -758,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116795258</v>
+        <v>120136625</v>
       </c>
       <c r="B3" t="n">
-        <v>78177</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -838,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>865140</v>
+        <v>865223</v>
       </c>
       <c r="R3" t="n">
-        <v>7411966</v>
+        <v>7411735</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -868,22 +854,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116795057</v>
+        <v>120136766</v>
       </c>
       <c r="B4" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>865055</v>
+        <v>865186</v>
       </c>
       <c r="R4" t="n">
-        <v>7411905</v>
+        <v>7411902</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -984,22 +955,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:53</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:53</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,15 +988,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116795106</v>
+        <v>120135690</v>
       </c>
       <c r="B5" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,21 +999,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>865096</v>
+        <v>865203</v>
       </c>
       <c r="R5" t="n">
-        <v>7411964</v>
+        <v>7411883</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1100,22 +1056,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,15 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116795451</v>
+        <v>120137034</v>
       </c>
       <c r="B6" t="n">
-        <v>78177</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>4412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1186,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>865183</v>
+        <v>865223</v>
       </c>
       <c r="R6" t="n">
-        <v>7411982</v>
+        <v>7411735</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1216,22 +1167,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,44 +1193,39 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>116795162</v>
+        <v>116794908</v>
       </c>
       <c r="B7" t="n">
-        <v>78176</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1302,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>865091</v>
+        <v>865086</v>
       </c>
       <c r="R7" t="n">
-        <v>7411750</v>
+        <v>7411963</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1337,7 +1273,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,7 +1283,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,43 +1311,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116795908</v>
+        <v>116795010</v>
       </c>
       <c r="B8" t="n">
-        <v>57294</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1419,10 +1349,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>865114</v>
+        <v>865168</v>
       </c>
       <c r="R8" t="n">
-        <v>7411745</v>
+        <v>7411766</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1454,7 +1384,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1464,12 +1394,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,6 +1403,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1496,37 +1422,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>116795485</v>
+        <v>116795057</v>
       </c>
       <c r="B9" t="n">
-        <v>78177</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1539,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>865156</v>
+        <v>865055</v>
       </c>
       <c r="R9" t="n">
-        <v>7411959</v>
+        <v>7411905</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1574,7 +1495,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1505,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1612,19 +1533,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>116794908</v>
+        <v>116795106</v>
       </c>
       <c r="B10" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1655,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>865086</v>
+        <v>865096</v>
       </c>
       <c r="R10" t="n">
-        <v>7411963</v>
+        <v>7411964</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1690,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1700,7 +1616,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,15 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>116795010</v>
+        <v>116795162</v>
       </c>
       <c r="B11" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,21 +1655,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1771,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>865168</v>
+        <v>865091</v>
       </c>
       <c r="R11" t="n">
-        <v>7411766</v>
+        <v>7411750</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1806,7 +1717,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1816,7 +1727,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1844,51 +1755,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117053323</v>
+        <v>116795790</v>
       </c>
       <c r="B12" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1896,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>865161</v>
+        <v>864981</v>
       </c>
       <c r="R12" t="n">
-        <v>7411891</v>
+        <v>7411767</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1926,12 +1824,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,7 +1853,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1959,51 +1871,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117053279</v>
+        <v>116795908</v>
       </c>
       <c r="B13" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2011,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>865167</v>
+        <v>865114</v>
       </c>
       <c r="R13" t="n">
-        <v>7411886</v>
+        <v>7411745</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2041,12 +1940,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2055,7 +1969,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2074,15 +1987,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117060139</v>
+        <v>117053279</v>
       </c>
       <c r="B14" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2109,12 +2017,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2126,10 +2034,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>865143</v>
+        <v>865167</v>
       </c>
       <c r="R14" t="n">
-        <v>7411903</v>
+        <v>7411886</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2177,27 +2085,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117053368</v>
+        <v>117053323</v>
       </c>
       <c r="B15" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2224,7 +2127,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2241,10 +2144,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>865164</v>
+        <v>865161</v>
       </c>
       <c r="R15" t="n">
-        <v>7411888</v>
+        <v>7411891</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2297,22 +2200,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117060432</v>
+        <v>117053368</v>
       </c>
       <c r="B16" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2339,7 +2237,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2356,10 +2254,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>865142</v>
+        <v>865164</v>
       </c>
       <c r="R16" t="n">
-        <v>7411907</v>
+        <v>7411888</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2407,27 +2305,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117060933</v>
+        <v>117060139</v>
       </c>
       <c r="B17" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2454,7 +2347,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2471,10 +2364,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>865141</v>
+        <v>865143</v>
       </c>
       <c r="R17" t="n">
-        <v>7411913</v>
+        <v>7411903</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2534,42 +2427,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120136766</v>
+        <v>117060432</v>
       </c>
       <c r="B18" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2577,10 +2474,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>865186</v>
+        <v>865142</v>
       </c>
       <c r="R18" t="n">
-        <v>7411902</v>
+        <v>7411907</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2607,12 +2504,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,54 +2525,58 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120135690</v>
+        <v>117060933</v>
       </c>
       <c r="B19" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2683,10 +2584,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>865203</v>
+        <v>865141</v>
       </c>
       <c r="R19" t="n">
-        <v>7411883</v>
+        <v>7411913</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2713,22 +2614,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2744,15 +2635,570 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>116795258</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kuuravaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>865140</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7411966</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
+      <c r="AX20" t="inlineStr">
         <is>
           <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>116795304</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kuuravaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>865229</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7411792</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk, Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>116795410</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kuuravaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>865233</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7411808</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk, Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>116795451</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kuuravaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>865183</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7411982</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk, Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>116795485</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kuuravaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>865156</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7411959</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk, Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 65184-2023 artfynd.xlsx
+++ b/artfynd/A 65184-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116796929</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120136625</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120136766</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120135690</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120137034</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116794908</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1419,6 +1454,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116795010</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1530,6 +1570,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116795057</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1641,6 +1686,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116795106</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1752,6 +1802,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116795162</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1868,6 +1923,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116795790</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1984,6 +2044,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116795908</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2094,6 +2159,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117053279</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2204,6 +2274,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117053323</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2314,6 +2389,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117053368</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2424,6 +2504,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117060139</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2534,6 +2619,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117060432</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2644,6 +2734,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117060933</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2755,6 +2850,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116795258</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2866,6 +2966,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116795304</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2977,6 +3082,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116795410</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3088,6 +3198,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116795451</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3199,8 +3314,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116795485</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>